--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105348_W1.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105348_W1.xlsx
@@ -570,64 +570,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8721</v>
+        <v>6.7891</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2453</v>
+        <v>4.2402</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6267</v>
+        <v>2.549</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9368</v>
+        <v>4.8624</v>
       </c>
       <c r="H2" t="n">
-        <v>2.274</v>
+        <v>2.2049</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6628</v>
+        <v>2.6576</v>
       </c>
       <c r="J2" t="n">
-        <v>5.3746</v>
+        <v>5.4716</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7771</v>
+        <v>1.7903</v>
       </c>
       <c r="L2" t="n">
-        <v>3.5976</v>
+        <v>3.6813</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4378</v>
+        <v>-0.6092</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4969</v>
+        <v>0.4146</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9348</v>
+        <v>-1.0238</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.4613</v>
+        <v>-3.4424</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2306</v>
+        <v>3.2129</v>
       </c>
       <c r="S2" t="n">
-        <v>0.012</v>
+        <v>-0.0078</v>
       </c>
       <c r="T2" t="n">
-        <v>0.178</v>
+        <v>0.0469</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.166</v>
+        <v>-0.0548</v>
       </c>
       <c r="V2" t="n">
-        <v>2.154</v>
+        <v>2.164</v>
       </c>
       <c r="W2" t="n">
-        <v>2.154</v>
+        <v>2.164</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1113</v>
+        <v>4.1171</v>
       </c>
       <c r="E3" t="n">
-        <v>4.509</v>
+        <v>4.563</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3977</v>
+        <v>-0.4459</v>
       </c>
       <c r="G3" t="n">
-        <v>4.171</v>
+        <v>4.1403</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2147</v>
+        <v>3.2308</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9563</v>
+        <v>0.9095</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9011</v>
+        <v>4.038</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3793</v>
+        <v>2.4752</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5218</v>
+        <v>1.5628</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2699</v>
+        <v>0.1023</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8354</v>
+        <v>0.7556</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5655</v>
+        <v>-0.6533</v>
       </c>
       <c r="P3" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6405</v>
+        <v>0.695</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.1669</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7173</v>
+        <v>0.8619</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.5462</v>
+        <v>-2.5542</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6847</v>
+        <v>0.6919</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.2309</v>
+        <v>-3.2461</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0011</v>
+        <v>3.925</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2656</v>
+        <v>3.2557</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7355</v>
+        <v>0.6693</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2913</v>
+        <v>1.2289</v>
       </c>
       <c r="H4" t="n">
-        <v>0.249</v>
+        <v>0.2117</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0423</v>
+        <v>1.0173</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2022</v>
+        <v>2.2849</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0895</v>
+        <v>0.1293</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1126</v>
+        <v>2.1556</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9109</v>
+        <v>-1.056</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1594</v>
+        <v>0.0824</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0703</v>
+        <v>-1.1383</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5383</v>
+        <v>2.5244</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5383</v>
+        <v>2.5244</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5132</v>
+        <v>-0.5203</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1597</v>
+        <v>-0.2621</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3535</v>
+        <v>-0.2582</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6847</v>
+        <v>0.6919</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2232</v>
+        <v>1.2329</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5385</v>
+        <v>-0.541</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0792</v>
+        <v>2.0386</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6214</v>
+        <v>3.6496</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5422</v>
+        <v>-1.6111</v>
       </c>
       <c r="G5" t="n">
-        <v>0.492</v>
+        <v>0.4897</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0508</v>
+        <v>2.0896</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5588</v>
+        <v>-1.5998</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5087</v>
+        <v>2.6396</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0577</v>
+        <v>2.1513</v>
       </c>
       <c r="L5" t="n">
-        <v>0.451</v>
+        <v>0.4883</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0167</v>
+        <v>-2.1499</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0069</v>
+        <v>-0.0617</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0098</v>
+        <v>-2.0881</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0768</v>
+        <v>2.0655</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0768</v>
+        <v>2.0655</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0973</v>
+        <v>-0.1265</v>
       </c>
       <c r="T5" t="n">
-        <v>0.428</v>
+        <v>0.3182</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5253</v>
+        <v>-0.4446</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3923</v>
+        <v>-0.3901</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6847</v>
+        <v>0.6919</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1994</v>
+        <v>1.089</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6042</v>
+        <v>-0.6209</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8037</v>
+        <v>1.71</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4936</v>
+        <v>0.4079</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5583</v>
+        <v>3.4831</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.0647</v>
+        <v>-3.0752</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3978</v>
+        <v>1.5201</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5556</v>
+        <v>2.5746</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1578</v>
+        <v>-1.0545</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9043</v>
+        <v>-1.1123</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0027</v>
+        <v>0.9084</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.907</v>
+        <v>-2.0207</v>
       </c>
       <c r="P6" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2306</v>
+        <v>3.2129</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4675</v>
+        <v>0.4551</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3054</v>
+        <v>0.1539</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1621</v>
+        <v>0.3012</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6847</v>
+        <v>-0.6919</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6847</v>
+        <v>-0.6919</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,64 +985,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9784</v>
+        <v>-0.881</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6246</v>
+        <v>-2.4822</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6463</v>
+        <v>1.6012</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.0042</v>
+        <v>-4.8901</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5782</v>
+        <v>-1.4882</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.426</v>
+        <v>-3.402</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.6953</v>
+        <v>-3.4518</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9098</v>
+        <v>-1.7675</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.7855</v>
+        <v>-1.6843</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3089</v>
+        <v>-1.4383</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3316</v>
+        <v>0.2793</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6406</v>
+        <v>-1.7176</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7691</v>
+        <v>2.7539</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7691</v>
+        <v>2.7539</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.5633</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3859</v>
+        <v>0.2777</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1862</v>
+        <v>0.2856</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6847</v>
+        <v>0.6919</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6847</v>
+        <v>0.6919</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1068,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3053</v>
+        <v>-1.3307</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.3368</v>
+        <v>-3.3298</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0315</v>
+        <v>1.9991</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0456</v>
+        <v>-0.0268</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2436</v>
+        <v>1.1824</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1979</v>
+        <v>-1.2092</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6579</v>
+        <v>-0.585</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9139</v>
+        <v>0.9207</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5719</v>
+        <v>-1.5057</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7036</v>
+        <v>0.5582</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3297</v>
+        <v>0.2617</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3739</v>
+        <v>0.2966</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R8" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0336</v>
+        <v>0.073</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3713</v>
+        <v>-0.4499</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4049</v>
+        <v>0.5229</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4049</v>
+        <v>-1.382</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5404</v>
+        <v>-0.4739</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8645</v>
+        <v>-0.9081</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5395</v>
+        <v>-0.5214</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5899</v>
+        <v>1.5939</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1295</v>
+        <v>-2.1153</v>
       </c>
       <c r="J9" t="n">
-        <v>0.504</v>
+        <v>0.6227</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5958</v>
+        <v>1.6468</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.0919</v>
+        <v>-1.0241</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0435</v>
+        <v>-1.1441</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0059</v>
+        <v>-0.0529</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0376</v>
+        <v>-1.0912</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6923</v>
+        <v>-0.6885</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1731</v>
+        <v>-0.1721</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1094</v>
+        <v>0.0509</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2825</v>
+        <v>-0.223</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3503</v>
+        <v>-3.2424</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.2765</v>
+        <v>-5.1521</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9262</v>
+        <v>1.9096</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.0954</v>
+        <v>-3.995</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.5432</v>
+        <v>-4.3656</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4478</v>
+        <v>0.3707</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.1384</v>
+        <v>-4.903</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.2123</v>
+        <v>-4.9771</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0738</v>
+        <v>0.0741</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0431</v>
+        <v>0.9081</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6691</v>
+        <v>0.6115</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3739</v>
+        <v>0.2966</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R10" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5143</v>
+        <v>1.523</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0157</v>
+        <v>0.8984</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4986</v>
+        <v>0.6246</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5385</v>
+        <v>-0.541</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5385</v>
+        <v>-0.541</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,58 +1317,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7764</v>
+        <v>-5.6316</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.5004</v>
+        <v>-6.3358</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7239</v>
+        <v>0.7042</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.565</v>
+        <v>-3.4775</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1207</v>
+        <v>-2.0426</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4443</v>
+        <v>-1.4349</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.134</v>
+        <v>-3.93</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.4514</v>
+        <v>-2.3131</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.6826</v>
+        <v>-1.6169</v>
       </c>
       <c r="M11" t="n">
-        <v>0.569</v>
+        <v>0.4525</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3306</v>
+        <v>0.2705</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2384</v>
+        <v>0.182</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.846</v>
+        <v>-1.836</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3654</v>
+        <v>-0.3182</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0588</v>
+        <v>-0.1108</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3066</v>
+        <v>-0.2073</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.4478</v>
+        <v>5.491099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.241599999999999</v>
+        <v>-2.686199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>8.689399999999999</v>
+        <v>8.177300000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.773799999999998</v>
+        <v>-1.781599999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>5.938200000000002</v>
+        <v>6.100000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-7.712000000000002</v>
+        <v>-7.8813</v>
       </c>
       <c r="J12" t="n">
-        <v>2.262799999999999</v>
+        <v>3.707099999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>1.795399999999999</v>
+        <v>2.6305</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4670999999999996</v>
+        <v>1.076600000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.0365</v>
+        <v>-5.4887</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1426</v>
+        <v>3.4694</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.179399999999999</v>
+        <v>-8.957799999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>5.768799999999999</v>
+        <v>5.7373</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.6914</v>
+        <v>-12.6224</v>
       </c>
       <c r="R12" t="n">
-        <v>18.4604</v>
+        <v>18.3596</v>
       </c>
       <c r="S12" t="n">
-        <v>2.091</v>
+        <v>2.1645</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7558</v>
+        <v>0.7563</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3351999999999999</v>
+        <v>1.4083</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6382999999999999</v>
+        <v>-0.6293999999999997</v>
       </c>
       <c r="W12" t="n">
-        <v>5.4313</v>
+        <v>5.4726</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.0696</v>
+        <v>-6.102</v>
       </c>
       <c r="Y12" t="inlineStr"/>
     </row>
@@ -1479,67 +1479,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4453</v>
+        <v>4.3584</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3105</v>
+        <v>3.2874</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1348</v>
+        <v>1.071</v>
       </c>
       <c r="G13" t="n">
-        <v>4.84</v>
+        <v>4.7369</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3964</v>
+        <v>0.3211</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4436</v>
+        <v>4.4158</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5066</v>
+        <v>4.558</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0677</v>
+        <v>0.0682</v>
       </c>
       <c r="L13" t="n">
-        <v>4.4389</v>
+        <v>4.4898</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3334</v>
+        <v>0.1789</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3287</v>
+        <v>0.2529</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0047</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7716</v>
+        <v>-0.7589</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4963</v>
+        <v>-0.5855</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2753</v>
+        <v>-0.1734</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6847</v>
+        <v>0.6919</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5385</v>
+        <v>-0.541</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1562,67 +1562,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8188</v>
+        <v>2.7535</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7255</v>
+        <v>3.6849</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9067</v>
+        <v>-0.9314</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2577</v>
+        <v>2.1796</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0265</v>
+        <v>0.9872</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2311</v>
+        <v>1.1924</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7002</v>
+        <v>2.7149</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3709</v>
+        <v>1.3811</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3293</v>
+        <v>1.3338</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4425</v>
+        <v>-0.5353</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3444</v>
+        <v>-0.3939</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.1414</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6382</v>
+        <v>0.6559</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4868</v>
+        <v>0.429</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1513</v>
+        <v>0.2269</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5385</v>
+        <v>-0.541</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1645,67 +1645,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.635</v>
+        <v>2.6148</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6836</v>
+        <v>2.7181</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0486</v>
+        <v>-0.1033</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1531</v>
+        <v>2.1284</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.678</v>
+        <v>-0.6908</v>
       </c>
       <c r="I15" t="n">
-        <v>2.831</v>
+        <v>2.8192</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4947</v>
+        <v>2.6139</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8364</v>
+        <v>-0.7644</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3312</v>
+        <v>3.3783</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3417</v>
+        <v>-0.4855</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1585</v>
+        <v>0.0735</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5001</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="R15" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2103</v>
+        <v>-0.2021</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1189</v>
+        <v>-0.2073</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0915</v>
+        <v>0.0052</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5385</v>
+        <v>-0.541</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2714</v>
+        <v>2.2378</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9721</v>
+        <v>1.9571</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2993</v>
+        <v>0.2807</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2398</v>
+        <v>1.2061</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3564</v>
+        <v>-0.3669</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5962</v>
+        <v>1.573</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6139</v>
+        <v>1.6207</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3216</v>
+        <v>0.324</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2924</v>
+        <v>1.2968</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3742</v>
+        <v>-0.4146</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.678</v>
+        <v>-0.6908</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3038</v>
+        <v>0.2763</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6394</v>
+        <v>0.6415</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5889</v>
+        <v>0.5659</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0504</v>
+        <v>0.0756</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3923</v>
+        <v>0.3901</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3923</v>
+        <v>0.3901</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2518</v>
+        <v>1.2902</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2759</v>
+        <v>-0.1693</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5277</v>
+        <v>1.4594</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0435</v>
+        <v>0.1123</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3839</v>
+        <v>-1.3629</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4274</v>
+        <v>1.4752</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1554</v>
+        <v>0.3771</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8653999999999999</v>
+        <v>-0.7544</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0208</v>
+        <v>1.1315</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1119</v>
+        <v>-0.2648</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5185</v>
+        <v>-0.6085</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4066</v>
+        <v>0.3437</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2608</v>
+        <v>-0.2777</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4313</v>
+        <v>-0.5464</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1705</v>
+        <v>0.2686</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,64 +1894,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4829</v>
+        <v>0.4052</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.102</v>
+        <v>-2.1309</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5849</v>
+        <v>2.5361</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4321</v>
+        <v>1.3472</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3002</v>
+        <v>1.2864</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1318</v>
+        <v>0.0608</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2699</v>
+        <v>1.3564</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9745</v>
+        <v>1.06</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2954</v>
+        <v>0.2964</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1622</v>
+        <v>-0.0092</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3257</v>
+        <v>0.2264</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1636</v>
+        <v>-0.2356</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.9228</v>
+        <v>-3.9014</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.9996</v>
+        <v>-5.9669</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0768</v>
+        <v>2.0655</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8197</v>
+        <v>0.7954</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4737</v>
+        <v>0.3156</v>
       </c>
       <c r="U18" t="n">
-        <v>0.346</v>
+        <v>0.4799</v>
       </c>
       <c r="V18" t="n">
-        <v>2.154</v>
+        <v>2.164</v>
       </c>
       <c r="W18" t="n">
-        <v>2.154</v>
+        <v>2.164</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1977,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1849</v>
+        <v>-0.1767</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7824</v>
+        <v>-1.7093</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5975</v>
+        <v>1.5327</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.382</v>
+        <v>-1.3502</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0765</v>
+        <v>-0.1475</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3055</v>
+        <v>-1.2027</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3739</v>
+        <v>-1.1617</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.232</v>
+        <v>-0.1946</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1419</v>
+        <v>-0.9671</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0081</v>
+        <v>-0.1885</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1555</v>
+        <v>0.0471</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1636</v>
+        <v>-0.2356</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6153</v>
+        <v>1.6065</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4182</v>
+        <v>-0.4329</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4085</v>
+        <v>-0.5477</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0098</v>
+        <v>0.1147</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6974</v>
+        <v>-0.7077</v>
       </c>
       <c r="E20" t="n">
-        <v>0.242</v>
+        <v>0.2708</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9394</v>
+        <v>-0.9785</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4529</v>
+        <v>0.4486</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4994</v>
+        <v>1.4558</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0465</v>
+        <v>-1.0072</v>
       </c>
       <c r="J20" t="n">
-        <v>0.356</v>
+        <v>0.434</v>
       </c>
       <c r="K20" t="n">
-        <v>1.337</v>
+        <v>1.347</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9811</v>
+        <v>-0.9129</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0969</v>
+        <v>0.0146</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1624</v>
+        <v>0.1088</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0654</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R20" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1574</v>
+        <v>0.1552</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0372</v>
+        <v>-0.0978</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1946</v>
+        <v>0.253</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="W20" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.154</v>
+        <v>-2.164</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,40 +2143,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.064</v>
+        <v>-1.081</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8172</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2467</v>
+        <v>-0.2569</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0135</v>
+        <v>-1.0054</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1818</v>
+        <v>-1.1671</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1683</v>
+        <v>0.1617</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8413</v>
+        <v>-0.8084</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8413</v>
+        <v>-0.8084</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1722</v>
+        <v>-0.1969</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3405</v>
+        <v>-0.3586</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1683</v>
+        <v>0.1617</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2188,13 +2188,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0504</v>
+        <v>-0.0756</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0241</v>
+        <v>-0.0156</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0745</v>
+        <v>-0.06</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2226,58 +2226,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6861</v>
+        <v>-2.6652</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7463</v>
+        <v>-2.7049</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0602</v>
+        <v>0.0397</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8316</v>
+        <v>-1.8111</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4666</v>
+        <v>-1.4305</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.365</v>
+        <v>-0.3806</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.595</v>
+        <v>-1.5287</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.6319</v>
+        <v>-1.5657</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0369</v>
+        <v>0.0371</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2366</v>
+        <v>-0.2824</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1653</v>
+        <v>0.1352</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.402</v>
+        <v>-0.4176</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.923</v>
+        <v>-0.918</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S22" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0639</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0024</v>
+        <v>-0.0287</v>
       </c>
       <c r="U22" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0926</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2309,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4261</v>
+        <v>-5.3384</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.8996</v>
+        <v>-5.7443</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4735</v>
+        <v>0.4059</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1764</v>
+        <v>-2.0838</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6353</v>
+        <v>-2.6158</v>
       </c>
       <c r="I23" t="n">
-        <v>0.459</v>
+        <v>0.532</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3567</v>
+        <v>-1.1075</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.61</v>
+        <v>-1.5046</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2533</v>
+        <v>0.3971</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8196</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0253</v>
+        <v>-1.1112</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2057</v>
+        <v>0.1349</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.4613</v>
+        <v>-3.4424</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.6151</v>
+        <v>-4.5899</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2116</v>
+        <v>0.1878</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0722</v>
+        <v>-0.0469</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1393</v>
+        <v>0.2347</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.6747</v>
+        <v>-6.548</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.9997</v>
+        <v>-6.8129</v>
       </c>
       <c r="F24" t="n">
-        <v>0.325</v>
+        <v>0.2649</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.2418</v>
+        <v>-4.1273</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3824</v>
+        <v>-2.3689</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8593</v>
+        <v>-1.7584</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.8933</v>
+        <v>-3.5801</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.1975</v>
+        <v>-2.0573</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.6958</v>
+        <v>-1.5228</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3485</v>
+        <v>-0.5472</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1849</v>
+        <v>-0.3115</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1636</v>
+        <v>-0.2356</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.846</v>
+        <v>-1.836</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6921</v>
+        <v>-3.6719</v>
       </c>
       <c r="R24" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2945</v>
+        <v>-0.283</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4914</v>
+        <v>-0.6428</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1969</v>
+        <v>0.3599</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2924</v>
+        <v>-0.3017</v>
       </c>
       <c r="W24" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3694</v>
+        <v>-1.3838</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.828000000000001</v>
+        <v>-2.857100000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.689399999999999</v>
+        <v>-8.1774</v>
       </c>
       <c r="F25" t="n">
-        <v>5.861500000000001</v>
+        <v>5.3203</v>
       </c>
       <c r="G25" t="n">
-        <v>1.7738</v>
+        <v>1.781300000000002</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.9384</v>
+        <v>-6.0999</v>
       </c>
       <c r="I25" t="n">
-        <v>7.7121</v>
+        <v>7.8812</v>
       </c>
       <c r="J25" t="n">
-        <v>4.036499999999998</v>
+        <v>5.4886</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.142799999999999</v>
+        <v>-3.4691</v>
       </c>
       <c r="L25" t="n">
-        <v>8.179399999999999</v>
+        <v>8.958</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.2628</v>
+        <v>-3.7072</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.7955</v>
+        <v>-2.6306</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4672999999999999</v>
+        <v>-1.0764</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.7687</v>
+        <v>-5.7373</v>
       </c>
       <c r="Q25" t="n">
-        <v>-18.4605</v>
+        <v>-18.3597</v>
       </c>
       <c r="R25" t="n">
-        <v>12.6916</v>
+        <v>12.6225</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5289999999999999</v>
+        <v>0.4695</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3355</v>
+        <v>-1.4082</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8639999999999999</v>
+        <v>1.8777</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6384000000000001</v>
+        <v>0.6294</v>
       </c>
       <c r="W25" t="n">
-        <v>6.069699999999999</v>
+        <v>6.1019</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.431299999999999</v>
+        <v>-5.472600000000001</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105348_W1.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105348_W1.xlsx
@@ -570,64 +570,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7891</v>
+        <v>6.6958</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2402</v>
+        <v>3.9526</v>
       </c>
       <c r="F2" t="n">
-        <v>2.549</v>
+        <v>2.7432</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8624</v>
+        <v>4.8211</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2049</v>
+        <v>2.192</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6576</v>
+        <v>2.6291</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4716</v>
+        <v>5.3621</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7903</v>
+        <v>1.7433</v>
       </c>
       <c r="L2" t="n">
-        <v>3.6813</v>
+        <v>3.6188</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6092</v>
+        <v>-0.5411</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4146</v>
+        <v>0.4487</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0238</v>
+        <v>-0.9898</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.4424</v>
+        <v>-3.5096</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2129</v>
+        <v>3.2756</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0078</v>
+        <v>-0.0195</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0469</v>
+        <v>-0.0282</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0548</v>
+        <v>0.0086</v>
       </c>
       <c r="V2" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="W2" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1171</v>
+        <v>4.1494</v>
       </c>
       <c r="E3" t="n">
-        <v>4.563</v>
+        <v>4.3475</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4459</v>
+        <v>-0.198</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1403</v>
+        <v>4.0612</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2308</v>
+        <v>3.15</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9095</v>
+        <v>0.9112</v>
       </c>
       <c r="J3" t="n">
-        <v>4.038</v>
+        <v>3.9042</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4752</v>
+        <v>2.3693</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5628</v>
+        <v>1.5349</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1023</v>
+        <v>0.157</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7556</v>
+        <v>0.7808</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6533</v>
+        <v>-0.6237</v>
       </c>
       <c r="P3" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S3" t="n">
-        <v>0.695</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1669</v>
+        <v>-0.223</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8619</v>
+        <v>0.9655</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.5542</v>
+        <v>-2.526</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6919</v>
+        <v>0.6664</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.2461</v>
+        <v>-3.1923</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.925</v>
+        <v>3.9426</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2557</v>
+        <v>3.0969</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6693</v>
+        <v>0.8457</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2289</v>
+        <v>1.2388</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2117</v>
+        <v>0.2266</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0173</v>
+        <v>1.0122</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2849</v>
+        <v>2.226</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1293</v>
+        <v>0.1055</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1556</v>
+        <v>2.1205</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.056</v>
+        <v>-0.9872</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0824</v>
+        <v>0.1211</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1383</v>
+        <v>-1.1083</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5244</v>
+        <v>2.5737</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5244</v>
+        <v>2.5737</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5203</v>
+        <v>-0.5362</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2621</v>
+        <v>-0.3275</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2582</v>
+        <v>-0.2087</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6919</v>
+        <v>0.6664</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0386</v>
+        <v>2.0126</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6496</v>
+        <v>3.4552</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6111</v>
+        <v>-1.4426</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4897</v>
+        <v>0.4509</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0896</v>
+        <v>2.0224</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5998</v>
+        <v>-1.5715</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6396</v>
+        <v>2.5272</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1513</v>
+        <v>2.0538</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4883</v>
+        <v>0.4734</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1499</v>
+        <v>-2.0763</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0617</v>
+        <v>-0.0314</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0881</v>
+        <v>-2.0449</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1265</v>
+        <v>-0.1463</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3182</v>
+        <v>0.2616</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4446</v>
+        <v>-0.4079</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3901</v>
+        <v>-0.3978</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6919</v>
+        <v>0.6664</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.089</v>
+        <v>1.1345</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6209</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.71</v>
+        <v>1.9667</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4079</v>
+        <v>0.4068</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4831</v>
+        <v>3.4448</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.0752</v>
+        <v>-3.038</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5201</v>
+        <v>1.4382</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5746</v>
+        <v>2.507</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.0545</v>
+        <v>-1.0688</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1123</v>
+        <v>-1.0314</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9084</v>
+        <v>0.9378</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0207</v>
+        <v>-1.9693</v>
       </c>
       <c r="P6" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2129</v>
+        <v>3.2756</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4551</v>
+        <v>0.4582</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1539</v>
+        <v>0.0693</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3012</v>
+        <v>0.3889</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6919</v>
+        <v>-0.6664</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6919</v>
+        <v>-0.6664</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,64 +985,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.881</v>
+        <v>-0.8272</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4822</v>
+        <v>-2.6064</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6012</v>
+        <v>1.7792</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.8901</v>
+        <v>-4.8722</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4882</v>
+        <v>-1.5023</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.402</v>
+        <v>-3.3699</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.4518</v>
+        <v>-3.494</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7675</v>
+        <v>-1.8029</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.6843</v>
+        <v>-1.691</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4383</v>
+        <v>-1.3782</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2793</v>
+        <v>0.3006</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7176</v>
+        <v>-1.6789</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7539</v>
+        <v>2.8077</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7539</v>
+        <v>2.8077</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5633</v>
+        <v>0.571</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2777</v>
+        <v>0.2212</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2856</v>
+        <v>0.3498</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6919</v>
+        <v>0.6664</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6919</v>
+        <v>0.6664</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1068,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3307</v>
+        <v>-1.3108</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.3298</v>
+        <v>-3.4545</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9991</v>
+        <v>2.1437</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0268</v>
+        <v>-0.0046</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1824</v>
+        <v>1.1882</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2092</v>
+        <v>-1.1928</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.585</v>
+        <v>-0.609</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9207</v>
+        <v>0.8966</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5057</v>
+        <v>-1.5056</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5582</v>
+        <v>0.6045</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2617</v>
+        <v>0.2917</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2966</v>
+        <v>0.3128</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R8" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S8" t="n">
-        <v>0.073</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4499</v>
+        <v>-0.5057</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5229</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.382</v>
+        <v>-1.4164</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4739</v>
+        <v>-0.5985</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9081</v>
+        <v>-0.8178</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5214</v>
+        <v>-0.539</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5939</v>
+        <v>1.5562</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1153</v>
+        <v>-2.0951</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6227</v>
+        <v>0.5534</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6468</v>
+        <v>1.5831</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.0241</v>
+        <v>-1.0297</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1441</v>
+        <v>-1.0923</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0529</v>
+        <v>-0.0269</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0912</v>
+        <v>-1.0654</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6885</v>
+        <v>-0.7019</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R9" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1721</v>
+        <v>-0.1755</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0509</v>
+        <v>0.018</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.223</v>
+        <v>-0.1934</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2424</v>
+        <v>-3.1789</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.1521</v>
+        <v>-5.2357</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9096</v>
+        <v>2.0568</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.995</v>
+        <v>-3.9755</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.3656</v>
+        <v>-4.3615</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3707</v>
+        <v>0.386</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.903</v>
+        <v>-4.9165</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.9771</v>
+        <v>-4.9897</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0741</v>
+        <v>0.0732</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9081</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6115</v>
+        <v>0.6282</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2966</v>
+        <v>0.3128</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R10" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S10" t="n">
-        <v>1.523</v>
+        <v>1.5626</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8984</v>
+        <v>0.8507</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6246</v>
+        <v>0.712</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,58 +1317,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6316</v>
+        <v>-5.629</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.3358</v>
+        <v>-6.4329</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7042</v>
+        <v>0.804</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4775</v>
+        <v>-3.4592</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0426</v>
+        <v>-2.0381</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4349</v>
+        <v>-1.4212</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.93</v>
+        <v>-3.9496</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.3131</v>
+        <v>-2.3342</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.6169</v>
+        <v>-1.6154</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4525</v>
+        <v>0.4904</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2705</v>
+        <v>0.2961</v>
       </c>
       <c r="O11" t="n">
-        <v>0.182</v>
+        <v>0.1942</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.836</v>
+        <v>-1.8718</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R11" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3182</v>
+        <v>-0.2979</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1108</v>
+        <v>-0.1436</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2073</v>
+        <v>-0.1544</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.491099999999999</v>
+        <v>5.5726</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.686199999999999</v>
+        <v>-4.308</v>
       </c>
       <c r="F12" t="n">
-        <v>8.177300000000001</v>
+        <v>9.880899999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.781599999999999</v>
+        <v>-1.871699999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>6.100000000000001</v>
+        <v>5.8783</v>
       </c>
       <c r="I12" t="n">
-        <v>-7.8813</v>
+        <v>-7.75</v>
       </c>
       <c r="J12" t="n">
-        <v>3.707099999999999</v>
+        <v>3.041999999999997</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6305</v>
+        <v>2.1318</v>
       </c>
       <c r="L12" t="n">
-        <v>1.076600000000001</v>
+        <v>0.9102999999999988</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.4887</v>
+        <v>-4.913600000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4694</v>
+        <v>3.7467</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.957799999999999</v>
+        <v>-8.660500000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>5.7373</v>
+        <v>5.849299999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.6224</v>
+        <v>-12.8685</v>
       </c>
       <c r="R12" t="n">
-        <v>18.3596</v>
+        <v>18.7177</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1645</v>
+        <v>2.2564</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7563</v>
+        <v>0.1928</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4083</v>
+        <v>2.0637</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6293999999999997</v>
+        <v>-0.6612999999999998</v>
       </c>
       <c r="W12" t="n">
-        <v>5.4726</v>
+        <v>5.3258</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.102</v>
+        <v>-5.987</v>
       </c>
       <c r="Y12" t="inlineStr"/>
     </row>
@@ -1479,67 +1479,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3584</v>
+        <v>4.3264</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2874</v>
+        <v>3.1048</v>
       </c>
       <c r="F13" t="n">
-        <v>1.071</v>
+        <v>1.2216</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7369</v>
+        <v>4.7269</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3211</v>
+        <v>0.3536</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4158</v>
+        <v>4.3733</v>
       </c>
       <c r="J13" t="n">
-        <v>4.558</v>
+        <v>4.4929</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0682</v>
+        <v>0.0664</v>
       </c>
       <c r="L13" t="n">
-        <v>4.4898</v>
+        <v>4.4265</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1789</v>
+        <v>0.234</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2529</v>
+        <v>0.2872</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0532</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7589</v>
+        <v>-0.7687</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5855</v>
+        <v>-0.6506</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1734</v>
+        <v>-0.1181</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6919</v>
+        <v>0.6664</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1562,67 +1562,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7535</v>
+        <v>2.7916</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6849</v>
+        <v>3.5997</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9314</v>
+        <v>-0.8081</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1796</v>
+        <v>2.1747</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9872</v>
+        <v>0.9858</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1924</v>
+        <v>1.1889</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7149</v>
+        <v>2.6625</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3811</v>
+        <v>1.3448</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3338</v>
+        <v>1.3177</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5353</v>
+        <v>-0.4878</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3939</v>
+        <v>-0.359</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1414</v>
+        <v>-0.1289</v>
       </c>
       <c r="P14" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6559</v>
+        <v>0.6811</v>
       </c>
       <c r="T14" t="n">
-        <v>0.429</v>
+        <v>0.4051</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2269</v>
+        <v>0.2759</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="W14" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1645,67 +1645,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6148</v>
+        <v>2.622</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7181</v>
+        <v>2.5778</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1033</v>
+        <v>0.0442</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1284</v>
+        <v>2.122</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6908</v>
+        <v>-0.6686</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8192</v>
+        <v>2.7906</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6139</v>
+        <v>2.5432</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7644</v>
+        <v>-0.7852</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3783</v>
+        <v>3.3284</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4855</v>
+        <v>-0.4212</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0735</v>
+        <v>0.1166</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R15" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2021</v>
+        <v>-0.2019</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2073</v>
+        <v>-0.2634</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0052</v>
+        <v>0.0615</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2378</v>
+        <v>2.2632</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9571</v>
+        <v>1.928</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2807</v>
+        <v>0.3352</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2061</v>
+        <v>1.2081</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3669</v>
+        <v>-0.3531</v>
       </c>
       <c r="I16" t="n">
-        <v>1.573</v>
+        <v>1.5612</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6207</v>
+        <v>1.5966</v>
       </c>
       <c r="K16" t="n">
-        <v>0.324</v>
+        <v>0.3155</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2968</v>
+        <v>1.2811</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4146</v>
+        <v>-0.3885</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6908</v>
+        <v>-0.6686</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2763</v>
+        <v>0.2801</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6415</v>
+        <v>0.6574</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5659</v>
+        <v>0.5654</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0756</v>
+        <v>0.092</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3901</v>
+        <v>0.3978</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3901</v>
+        <v>0.3978</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2902</v>
+        <v>1.3127</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1693</v>
+        <v>-0.3308</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4594</v>
+        <v>1.6435</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1123</v>
+        <v>0.1031</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3629</v>
+        <v>-1.3435</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4752</v>
+        <v>1.4466</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3771</v>
+        <v>0.2948</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7544</v>
+        <v>-0.796</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1315</v>
+        <v>1.0908</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2648</v>
+        <v>-0.1917</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6085</v>
+        <v>-0.5475</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3437</v>
+        <v>0.3558</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2777</v>
+        <v>-0.2939</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5464</v>
+        <v>-0.6256</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2686</v>
+        <v>0.3317</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,64 +1894,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4052</v>
+        <v>0.2931</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1309</v>
+        <v>-2.4402</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5361</v>
+        <v>2.7332</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3472</v>
+        <v>1.343</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2864</v>
+        <v>1.2649</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0608</v>
+        <v>0.0781</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3564</v>
+        <v>1.2841</v>
       </c>
       <c r="K18" t="n">
-        <v>1.06</v>
+        <v>0.9913</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2964</v>
+        <v>0.2928</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0092</v>
+        <v>0.0589</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2264</v>
+        <v>0.2737</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2356</v>
+        <v>-0.2148</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.9014</v>
+        <v>-3.9775</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.9669</v>
+        <v>-6.0833</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7954</v>
+        <v>0.7994</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3156</v>
+        <v>0.2308</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4799</v>
+        <v>0.5685</v>
       </c>
       <c r="V18" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="W18" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1977,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1767</v>
+        <v>-0.1355</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7093</v>
+        <v>-1.8514</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5327</v>
+        <v>1.7159</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3502</v>
+        <v>-1.322</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1475</v>
+        <v>-0.1068</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2027</v>
+        <v>-1.2152</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1617</v>
+        <v>-1.2104</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1946</v>
+        <v>-0.21</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.9671</v>
+        <v>-1.0004</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1885</v>
+        <v>-0.1116</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0471</v>
+        <v>0.1032</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2356</v>
+        <v>-0.2148</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4329</v>
+        <v>-0.4513</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5477</v>
+        <v>-0.641</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1147</v>
+        <v>0.1897</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7077</v>
+        <v>-0.7003</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2708</v>
+        <v>0.1507</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9785</v>
+        <v>-0.851</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4486</v>
+        <v>0.4404</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4558</v>
+        <v>1.4462</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0072</v>
+        <v>-1.0058</v>
       </c>
       <c r="J20" t="n">
-        <v>0.434</v>
+        <v>0.3917</v>
       </c>
       <c r="K20" t="n">
-        <v>1.347</v>
+        <v>1.3116</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9129</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0146</v>
+        <v>0.0487</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1088</v>
+        <v>0.1346</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0859</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R20" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1552</v>
+        <v>0.1574</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0978</v>
+        <v>-0.1352</v>
       </c>
       <c r="U20" t="n">
-        <v>0.253</v>
+        <v>0.2926</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W20" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,40 +2143,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.081</v>
+        <v>-1.0792</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.8468</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2569</v>
+        <v>-0.2324</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0054</v>
+        <v>-0.9872</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1671</v>
+        <v>-1.1487</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1617</v>
+        <v>0.1615</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8084</v>
+        <v>-0.8077</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8084</v>
+        <v>-0.8077</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1969</v>
+        <v>-0.1795</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3586</v>
+        <v>-0.341</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1617</v>
+        <v>0.1615</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2188,13 +2188,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0756</v>
+        <v>-0.092</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0156</v>
+        <v>-0.0391</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.06</v>
+        <v>-0.0529</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2226,58 +2226,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6652</v>
+        <v>-2.6631</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7049</v>
+        <v>-2.7463</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0397</v>
+        <v>0.0832</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8111</v>
+        <v>-1.7899</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4305</v>
+        <v>-1.4175</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3806</v>
+        <v>-0.3724</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5287</v>
+        <v>-1.529</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.5657</v>
+        <v>-1.5656</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0371</v>
+        <v>0.0366</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2824</v>
+        <v>-0.2609</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1352</v>
+        <v>0.1481</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4176</v>
+        <v>-0.409</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.918</v>
+        <v>-0.9359</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0639</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0287</v>
+        <v>-0.0474</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0926</v>
+        <v>0.1101</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2309,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3384</v>
+        <v>-5.3914</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.7443</v>
+        <v>-5.9669</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4059</v>
+        <v>0.5756</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0838</v>
+        <v>-2.06</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6158</v>
+        <v>-2.5676</v>
       </c>
       <c r="I23" t="n">
-        <v>0.532</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1075</v>
+        <v>-1.1702</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5046</v>
+        <v>-1.5265</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3971</v>
+        <v>0.3563</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.8898</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1112</v>
+        <v>-1.0411</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1349</v>
+        <v>0.1513</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.4424</v>
+        <v>-3.5096</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5899</v>
+        <v>-4.6794</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1878</v>
+        <v>0.1782</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0469</v>
+        <v>-0.1173</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2347</v>
+        <v>0.2955</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.548</v>
+        <v>-6.5103</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.8129</v>
+        <v>-7.0596</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2649</v>
+        <v>0.5492</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.1273</v>
+        <v>-4.0873</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3689</v>
+        <v>-2.323</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7584</v>
+        <v>-1.7642</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.5801</v>
+        <v>-3.6347</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.0573</v>
+        <v>-2.0852</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.5228</v>
+        <v>-1.5495</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5472</v>
+        <v>-0.4526</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3115</v>
+        <v>-0.2379</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2356</v>
+        <v>-0.2148</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.836</v>
+        <v>-1.8718</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6719</v>
+        <v>-3.7436</v>
       </c>
       <c r="R24" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.283</v>
+        <v>-0.2827</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6428</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3599</v>
+        <v>0.4628</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3017</v>
+        <v>-0.2686</v>
       </c>
       <c r="W24" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3838</v>
+        <v>-1.3327</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.857100000000001</v>
+        <v>-2.870800000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.1774</v>
+        <v>-9.881</v>
       </c>
       <c r="F25" t="n">
-        <v>5.3203</v>
+        <v>7.010099999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>1.781300000000002</v>
+        <v>1.871800000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.0999</v>
+        <v>-5.8783</v>
       </c>
       <c r="I25" t="n">
-        <v>7.8812</v>
+        <v>7.7502</v>
       </c>
       <c r="J25" t="n">
-        <v>5.4886</v>
+        <v>4.9138</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.4691</v>
+        <v>-3.7466</v>
       </c>
       <c r="L25" t="n">
-        <v>8.958</v>
+        <v>8.660399999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.7072</v>
+        <v>-3.042</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.6306</v>
+        <v>-2.131699999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0764</v>
+        <v>-0.9105</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.7373</v>
+        <v>-5.849399999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-18.3597</v>
+        <v>-18.7179</v>
       </c>
       <c r="R25" t="n">
-        <v>12.6225</v>
+        <v>12.8685</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4695</v>
+        <v>0.4457000000000002</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.4082</v>
+        <v>-2.0638</v>
       </c>
       <c r="U25" t="n">
-        <v>1.8777</v>
+        <v>2.5093</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6294</v>
+        <v>0.6612</v>
       </c>
       <c r="W25" t="n">
-        <v>6.1019</v>
+        <v>5.987</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.472600000000001</v>
+        <v>-5.3257</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105348_W1.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105348_W1.xlsx
@@ -570,64 +570,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6958</v>
+        <v>6.763</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9526</v>
+        <v>4.0964</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7432</v>
+        <v>2.6666</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8211</v>
+        <v>4.8603</v>
       </c>
       <c r="H2" t="n">
-        <v>2.192</v>
+        <v>2.2158</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6291</v>
+        <v>2.6445</v>
       </c>
       <c r="J2" t="n">
-        <v>5.3621</v>
+        <v>5.3919</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7433</v>
+        <v>1.7632</v>
       </c>
       <c r="L2" t="n">
-        <v>3.6188</v>
+        <v>3.6286</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5411</v>
+        <v>-0.5316</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4487</v>
+        <v>0.4526</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9898</v>
+        <v>-0.9841</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.5096</v>
+        <v>-3.4811</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2756</v>
+        <v>3.249</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0195</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0282</v>
+        <v>0.0422</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0086</v>
+        <v>-0.0509</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1494</v>
+        <v>4.1319</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3475</v>
+        <v>4.4406</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.198</v>
+        <v>-0.3087</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0612</v>
+        <v>4.1081</v>
       </c>
       <c r="H3" t="n">
-        <v>3.15</v>
+        <v>3.186</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9112</v>
+        <v>0.9222</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9042</v>
+        <v>3.9359</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3693</v>
+        <v>2.3975</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5349</v>
+        <v>1.5384</v>
       </c>
       <c r="M3" t="n">
-        <v>0.157</v>
+        <v>0.1722</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7808</v>
+        <v>0.7884</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6237</v>
+        <v>-0.6162</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7052</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.223</v>
+        <v>-0.1725</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9655</v>
+        <v>0.8776</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.526</v>
+        <v>-2.5379</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6664</v>
+        <v>0.6772</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.1923</v>
+        <v>-3.2151</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9426</v>
+        <v>3.9531</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0969</v>
+        <v>3.1781</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8457</v>
+        <v>0.775</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2388</v>
+        <v>1.2496</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2266</v>
+        <v>0.2286</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0122</v>
+        <v>1.021</v>
       </c>
       <c r="J4" t="n">
-        <v>2.226</v>
+        <v>2.2343</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1055</v>
+        <v>0.1072</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1205</v>
+        <v>2.1271</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9872</v>
+        <v>-0.9847</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1211</v>
+        <v>0.1214</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1083</v>
+        <v>-1.106</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5737</v>
+        <v>2.5528</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5737</v>
+        <v>2.5528</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5362</v>
+        <v>-0.5265</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3275</v>
+        <v>-0.2692</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2087</v>
+        <v>-0.2573</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6664</v>
+        <v>0.6772</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1984</v>
+        <v>1.213</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5321</v>
+        <v>-0.5359</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0126</v>
+        <v>2.0357</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4552</v>
+        <v>3.5444</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4426</v>
+        <v>-1.5087</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4509</v>
+        <v>0.4707</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0224</v>
+        <v>2.0459</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5715</v>
+        <v>-1.5752</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5272</v>
+        <v>2.5499</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0538</v>
+        <v>2.0785</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4734</v>
+        <v>0.4714</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0763</v>
+        <v>-2.0791</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0314</v>
+        <v>-0.0326</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0449</v>
+        <v>-2.0465</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1057</v>
+        <v>2.0886</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1057</v>
+        <v>2.0886</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1463</v>
+        <v>-0.1291</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2616</v>
+        <v>0.3173</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4079</v>
+        <v>-0.4465</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3978</v>
+        <v>-0.3945</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6664</v>
+        <v>0.6772</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1345</v>
+        <v>1.1399</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9667</v>
+        <v>1.8631</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4068</v>
+        <v>0.429</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4448</v>
+        <v>3.4828</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.038</v>
+        <v>-3.0538</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4382</v>
+        <v>1.4479</v>
       </c>
       <c r="K6" t="n">
-        <v>2.507</v>
+        <v>2.5357</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.0688</v>
+        <v>-1.0878</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0314</v>
+        <v>-1.019</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9378</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.9693</v>
+        <v>-1.966</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2756</v>
+        <v>3.249</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4582</v>
+        <v>0.4598</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0693</v>
+        <v>0.1495</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3889</v>
+        <v>0.3103</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6664</v>
+        <v>-0.6772</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6664</v>
+        <v>-0.6772</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,64 +985,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8272</v>
+        <v>-0.8784</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6064</v>
+        <v>-2.5808</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7792</v>
+        <v>1.7024</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.8722</v>
+        <v>-4.9099</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5023</v>
+        <v>-1.518</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.3699</v>
+        <v>-3.3919</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.494</v>
+        <v>-3.5345</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.8029</v>
+        <v>-1.8213</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.691</v>
+        <v>-1.7133</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3782</v>
+        <v>-1.3753</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3006</v>
+        <v>0.3033</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6789</v>
+        <v>-1.6786</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8077</v>
+        <v>2.7849</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8077</v>
+        <v>2.7849</v>
       </c>
       <c r="S7" t="n">
-        <v>0.571</v>
+        <v>0.5694</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2212</v>
+        <v>0.2765</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3498</v>
+        <v>0.2929</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6664</v>
+        <v>0.6772</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6664</v>
+        <v>0.6772</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1068,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3108</v>
+        <v>-1.3143</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.4545</v>
+        <v>-3.3945</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1437</v>
+        <v>2.0802</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0046</v>
+        <v>0.0027</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1882</v>
+        <v>1.2008</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1928</v>
+        <v>-1.1981</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.609</v>
+        <v>-0.6155</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8966</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5056</v>
+        <v>-1.5224</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6045</v>
+        <v>0.6183</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2917</v>
+        <v>0.294</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3128</v>
+        <v>0.3243</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S8" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0755</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5057</v>
+        <v>-0.4582</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.5337</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1151,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4164</v>
+        <v>-1.4051</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5985</v>
+        <v>-0.5536</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8178</v>
+        <v>-0.8515</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.539</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5562</v>
+        <v>1.5739</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0951</v>
+        <v>-2.1087</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5534</v>
+        <v>0.5577</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5831</v>
+        <v>1.6018</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.0297</v>
+        <v>-1.0441</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0923</v>
+        <v>-1.0926</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0269</v>
+        <v>-0.0279</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0654</v>
+        <v>-1.0647</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7019</v>
+        <v>-0.6962</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1755</v>
+        <v>-0.1741</v>
       </c>
       <c r="T9" t="n">
-        <v>0.018</v>
+        <v>0.0491</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1934</v>
+        <v>-0.2231</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1789</v>
+        <v>-3.2376</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.2357</v>
+        <v>-5.2257</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0568</v>
+        <v>1.9881</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.9755</v>
+        <v>-4.0105</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.3615</v>
+        <v>-4.4084</v>
       </c>
       <c r="I10" t="n">
-        <v>0.386</v>
+        <v>0.3979</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.9165</v>
+        <v>-4.9693</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.9897</v>
+        <v>-5.0429</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0732</v>
+        <v>0.0736</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9588</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6282</v>
+        <v>0.6345</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3128</v>
+        <v>0.3243</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5626</v>
+        <v>1.5408</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8507</v>
+        <v>0.9039</v>
       </c>
       <c r="U10" t="n">
-        <v>0.712</v>
+        <v>0.6369</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5321</v>
+        <v>-0.5359</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5321</v>
+        <v>-0.5359</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,58 +1317,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.629</v>
+        <v>-5.6668</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.4329</v>
+        <v>-6.4263</v>
       </c>
       <c r="F11" t="n">
-        <v>0.804</v>
+        <v>0.7595</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4592</v>
+        <v>-3.4904</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0381</v>
+        <v>-2.06</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4212</v>
+        <v>-1.4303</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.9496</v>
+        <v>-3.9914</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.3342</v>
+        <v>-2.3587</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.6154</v>
+        <v>-1.6327</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4904</v>
+        <v>0.501</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2961</v>
+        <v>0.2986</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1942</v>
+        <v>0.2024</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8718</v>
+        <v>-1.8566</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2979</v>
+        <v>-0.3199</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1436</v>
+        <v>-0.1142</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1544</v>
+        <v>-0.2057</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.5726</v>
+        <v>5.521399999999996</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.308</v>
+        <v>-3.644700000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>9.880899999999999</v>
+        <v>9.165999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.871699999999999</v>
+        <v>-1.825200000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>5.8783</v>
+        <v>5.9474</v>
       </c>
       <c r="I12" t="n">
-        <v>-7.75</v>
+        <v>-7.772400000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>3.041999999999997</v>
+        <v>3.006900000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1318</v>
+        <v>2.167800000000002</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9102999999999988</v>
+        <v>0.8387999999999998</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.913600000000001</v>
+        <v>-4.832</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7467</v>
+        <v>3.7794</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.660500000000001</v>
+        <v>-8.611099999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>5.849299999999999</v>
+        <v>5.8018</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.8685</v>
+        <v>-12.764</v>
       </c>
       <c r="R12" t="n">
-        <v>18.7177</v>
+        <v>18.5657</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2564</v>
+        <v>2.1924</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1928</v>
+        <v>0.7244000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>2.0637</v>
+        <v>1.4679</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6612999999999998</v>
+        <v>-0.6476999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>5.3258</v>
+        <v>5.388000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.987</v>
+        <v>-6.0358</v>
       </c>
       <c r="Y12" t="inlineStr"/>
     </row>
@@ -1479,67 +1479,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3264</v>
+        <v>4.3642</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1048</v>
+        <v>3.2011</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2216</v>
+        <v>1.1631</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7269</v>
+        <v>4.7579</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3536</v>
+        <v>0.3565</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3733</v>
+        <v>4.4014</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4929</v>
+        <v>4.5122</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0664</v>
+        <v>0.0672</v>
       </c>
       <c r="L13" t="n">
-        <v>4.4265</v>
+        <v>4.445</v>
       </c>
       <c r="M13" t="n">
-        <v>0.234</v>
+        <v>0.2457</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2872</v>
+        <v>0.2893</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0532</v>
+        <v>-0.0436</v>
       </c>
       <c r="P13" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7687</v>
+        <v>-0.7671</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6506</v>
+        <v>-0.5958</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1181</v>
+        <v>-0.1713</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6664</v>
+        <v>0.6772</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5321</v>
+        <v>-0.5359</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1562,67 +1562,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7916</v>
+        <v>2.7892</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5997</v>
+        <v>3.6522</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8081</v>
+        <v>-0.8629</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1747</v>
+        <v>2.1968</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9858</v>
+        <v>0.9964</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1889</v>
+        <v>1.2004</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6625</v>
+        <v>2.6848</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3448</v>
+        <v>1.3602</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3177</v>
+        <v>1.3245</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4878</v>
+        <v>-0.4879</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.359</v>
+        <v>-0.3638</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1289</v>
+        <v>-0.1241</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6811</v>
+        <v>0.6641</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4051</v>
+        <v>0.4316</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2759</v>
+        <v>0.2326</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5321</v>
+        <v>-0.5359</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5321</v>
+        <v>0.5359</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1645,67 +1645,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.622</v>
+        <v>2.6235</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5778</v>
+        <v>2.6386</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0442</v>
+        <v>-0.0151</v>
       </c>
       <c r="G15" t="n">
-        <v>2.122</v>
+        <v>2.1314</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6686</v>
+        <v>-0.6764</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7906</v>
+        <v>2.8078</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5432</v>
+        <v>2.5481</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7852</v>
+        <v>-0.7931</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3284</v>
+        <v>3.3412</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4212</v>
+        <v>-0.4167</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1166</v>
+        <v>0.1167</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.5335</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2019</v>
+        <v>-0.2041</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2634</v>
+        <v>-0.2133</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0615</v>
+        <v>0.0092</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5321</v>
+        <v>0.5359</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5321</v>
+        <v>-0.5359</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2632</v>
+        <v>2.2591</v>
       </c>
       <c r="E16" t="n">
-        <v>1.928</v>
+        <v>1.9462</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3352</v>
+        <v>0.3129</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2081</v>
+        <v>1.2156</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3531</v>
+        <v>-0.3573</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5612</v>
+        <v>1.5729</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5966</v>
+        <v>1.6068</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3155</v>
+        <v>0.3191</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2811</v>
+        <v>1.2877</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3885</v>
+        <v>-0.3912</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6686</v>
+        <v>-0.6764</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2801</v>
+        <v>0.2852</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="R16" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6574</v>
+        <v>0.649</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5654</v>
+        <v>0.5715</v>
       </c>
       <c r="U16" t="n">
-        <v>0.092</v>
+        <v>0.0775</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3978</v>
+        <v>0.3945</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3978</v>
+        <v>0.3945</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3127</v>
+        <v>1.2918</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3308</v>
+        <v>-0.2777</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6435</v>
+        <v>1.5695</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1031</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3435</v>
+        <v>-1.3584</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4466</v>
+        <v>1.4487</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2948</v>
+        <v>0.2796</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.796</v>
+        <v>-0.8034</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0908</v>
+        <v>1.083</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1917</v>
+        <v>-0.1893</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5475</v>
+        <v>-0.555</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3558</v>
+        <v>0.3657</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2939</v>
+        <v>-0.2816</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6256</v>
+        <v>-0.5573</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3317</v>
+        <v>0.2757</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,64 +1894,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2931</v>
+        <v>0.3683</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4402</v>
+        <v>-2.2796</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7332</v>
+        <v>2.6479</v>
       </c>
       <c r="G18" t="n">
-        <v>1.343</v>
+        <v>1.3665</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2649</v>
+        <v>1.2791</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0781</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2841</v>
+        <v>1.2981</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9913</v>
+        <v>1.0037</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2928</v>
+        <v>0.2943</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0589</v>
+        <v>0.0684</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2737</v>
+        <v>0.2753</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2148</v>
+        <v>-0.2069</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.9775</v>
+        <v>-3.9452</v>
       </c>
       <c r="Q18" t="n">
-        <v>-6.0833</v>
+        <v>-6.0339</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1057</v>
+        <v>2.0886</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7994</v>
+        <v>0.8035</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2308</v>
+        <v>0.3128</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5685</v>
+        <v>0.4908</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1977,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1355</v>
+        <v>-0.158</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8514</v>
+        <v>-1.7994</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7159</v>
+        <v>1.6415</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.322</v>
+        <v>-1.344</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1068</v>
+        <v>-0.1091</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2152</v>
+        <v>-1.2349</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2104</v>
+        <v>-1.2399</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.21</v>
+        <v>-0.2118</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.0004</v>
+        <v>-1.028</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1116</v>
+        <v>-0.1041</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1032</v>
+        <v>0.1028</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2148</v>
+        <v>-0.2069</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4513</v>
+        <v>-0.4385</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.641</v>
+        <v>-0.5596</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1897</v>
+        <v>0.1211</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7003</v>
+        <v>-0.7014</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1507</v>
+        <v>0.2029</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.851</v>
+        <v>-0.9043</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4404</v>
+        <v>0.4455</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4462</v>
+        <v>1.462</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0058</v>
+        <v>-1.0164</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3917</v>
+        <v>0.393</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3116</v>
+        <v>1.3266</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9199000000000001</v>
+        <v>-0.9337</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0487</v>
+        <v>0.0526</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1346</v>
+        <v>0.1353</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0859</v>
+        <v>-0.0828</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1574</v>
+        <v>0.1569</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1352</v>
+        <v>-0.1014</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2926</v>
+        <v>0.2582</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1282</v>
+        <v>-2.1434</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,40 +2143,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0792</v>
+        <v>-1.0758</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8468</v>
+        <v>-0.8338</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2324</v>
+        <v>-0.242</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9872</v>
+        <v>-0.9983</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1487</v>
+        <v>-1.1615</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1615</v>
+        <v>0.1633</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8077</v>
+        <v>-0.8164</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8077</v>
+        <v>-0.8164</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1795</v>
+        <v>-0.1819</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.341</v>
+        <v>-0.3452</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1615</v>
+        <v>0.1633</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2188,13 +2188,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.092</v>
+        <v>-0.0775</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0391</v>
+        <v>-0.0174</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0529</v>
+        <v>-0.0601</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2226,58 +2226,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6631</v>
+        <v>-2.6694</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7463</v>
+        <v>-2.7362</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0832</v>
+        <v>0.0668</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7899</v>
+        <v>-1.8056</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4175</v>
+        <v>-1.4331</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3724</v>
+        <v>-0.3725</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.529</v>
+        <v>-1.5456</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.5656</v>
+        <v>-1.5824</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0366</v>
+        <v>0.0368</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2609</v>
+        <v>-0.26</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1481</v>
+        <v>0.1493</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.409</v>
+        <v>-0.4093</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9359</v>
+        <v>-0.9283</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R22" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0644</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0474</v>
+        <v>-0.0303</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1101</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2309,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3914</v>
+        <v>-5.3873</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.9669</v>
+        <v>-5.8958</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5756</v>
+        <v>0.5085</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.06</v>
+        <v>-2.0952</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5676</v>
+        <v>-2.5964</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5012</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1702</v>
+        <v>-1.2021</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5265</v>
+        <v>-1.5423</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3563</v>
+        <v>0.3402</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8898</v>
+        <v>-0.8931</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0411</v>
+        <v>-1.0541</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1513</v>
+        <v>0.161</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.5096</v>
+        <v>-3.4811</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.6794</v>
+        <v>-4.6414</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1782</v>
+        <v>0.189</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1173</v>
+        <v>-0.0523</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2955</v>
+        <v>0.2413</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.5103</v>
+        <v>-6.561</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.0596</v>
+        <v>-6.9845</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5492</v>
+        <v>0.4235</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.0873</v>
+        <v>-4.136</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.323</v>
+        <v>-2.3492</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7642</v>
+        <v>-1.7868</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.6347</v>
+        <v>-3.6867</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.0852</v>
+        <v>-2.1068</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.5495</v>
+        <v>-1.5799</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4526</v>
+        <v>-0.4493</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2379</v>
+        <v>-0.2424</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2148</v>
+        <v>-0.2069</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8718</v>
+        <v>-1.8566</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.7436</v>
+        <v>-3.7131</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="S24" t="n">
+        <v>-0.2857</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.6564</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="V24" t="n">
         <v>-0.2827</v>
       </c>
-      <c r="T24" t="n">
-        <v>-0.7455000000000001</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.4628</v>
-      </c>
-      <c r="V24" t="n">
-        <v>-0.2686</v>
-      </c>
       <c r="W24" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3327</v>
+        <v>-1.3544</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.870800000000001</v>
+        <v>-2.856799999999996</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.881</v>
+        <v>-9.166</v>
       </c>
       <c r="F25" t="n">
-        <v>7.010099999999999</v>
+        <v>6.309399999999998</v>
       </c>
       <c r="G25" t="n">
-        <v>1.871800000000001</v>
+        <v>1.824899999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.8783</v>
+        <v>-5.9474</v>
       </c>
       <c r="I25" t="n">
-        <v>7.7502</v>
+        <v>7.772500000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>4.9138</v>
+        <v>4.831900000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.7466</v>
+        <v>-3.779399999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>8.660399999999999</v>
+        <v>8.611099999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.042</v>
+        <v>-3.0068</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.131699999999999</v>
+        <v>-2.1682</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9105</v>
+        <v>-0.8387999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.849399999999999</v>
+        <v>-5.8019</v>
       </c>
       <c r="Q25" t="n">
-        <v>-18.7179</v>
+        <v>-18.5658</v>
       </c>
       <c r="R25" t="n">
-        <v>12.8685</v>
+        <v>12.764</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4457000000000002</v>
+        <v>0.4724</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.0638</v>
+        <v>-1.4679</v>
       </c>
       <c r="U25" t="n">
-        <v>2.5093</v>
+        <v>1.9403</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6612</v>
+        <v>0.6476</v>
       </c>
       <c r="W25" t="n">
-        <v>5.987</v>
+        <v>6.0358</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.3257</v>
+        <v>-5.388100000000001</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>
